--- a/Planning/LAUNCH/Progress_Tees_Valley_Weekly_Plan_Week07_12Oct.xlsx
+++ b/Planning/LAUNCH/Progress_Tees_Valley_Weekly_Plan_Week07_12Oct.xlsx
@@ -1154,7 +1154,7 @@
     <row r="8" ht="45.75" customHeight="1" s="48">
       <c r="A8" s="56" t="inlineStr">
         <is>
-          <t>SMSC/BV this week: BHM continues; Harvest window (tbc) — assembly carries it (Launch PSHE is rights-at-work interviews this week).  Hate Crime Awareness Week — if this week, tie to the BV Rule of Law assembly.  EVIDENCE: EFL: community/citizenship → log in the SMSC Evidence Tracker.</t>
+          <t>SMSC/BV this week: BHM continues; Harvest window (tbc) — assembly carries it (Launch PSHE is rights-at-work interviews this week).  Hate Crime Awareness Week — if this week, tie to the BV Rule of Law assembly.  EVIDENCE: evidence platform: community/citizenship → log in the SMSC Evidence Tracker.</t>
         </is>
       </c>
       <c r="B8" s="57" t="n"/>
@@ -1466,7 +1466,7 @@
       <c r="I13" s="69" t="inlineStr">
         <is>
           <t>TA rehearses each pupil before their interview; HoS gives one strength + one tip as live feedback; recordings feed both AQA UAS and PfA evidence.
-LOOP [Feedback Policy]: Voice = recorded micro-interview / script-flip / portfolio piece [VF] → Audience: listen fully, name one strength + one [NS] before tagging; then [R] → EVIDENCE: recording/portfolio to EFL, same day [E: PfA/careers/transition — weekly PfA minimum].</t>
+LOOP [Feedback Policy]: Voice = recorded micro-interview / script-flip / portfolio piece [VF] → Audience: listen fully, name one strength + one [NS] before tagging; then [R] → EVIDENCE: recording/portfolio to evidence platform, same day [E: PfA/careers/transition — weekly PfA minimum].</t>
         </is>
       </c>
       <c r="J13" s="69" t="inlineStr">
